--- a/Planificacion_Grupo03_E2.xlsx
+++ b/Planificacion_Grupo03_E2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\IW-GRUPO3-E2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D72A00F-2D61-4911-9973-570CD0276878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4047A1-2968-4061-BA0E-2D7081B569AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -463,7 +463,7 @@
     <col min="6" max="6" width="49.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +503,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -536,9 +536,11 @@
       <c r="D4" s="3">
         <v>46132</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="E4" s="3">
+        <v>46132</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">

--- a/Planificacion_Grupo03_E2.xlsx
+++ b/Planificacion_Grupo03_E2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\IW-GRUPO3-E2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4047A1-2968-4061-BA0E-2D7081B569AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C11D0F3-AB6A-46EB-8644-E87FCEB39ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t>Nº</t>
   </si>
@@ -64,6 +64,18 @@
   </si>
   <si>
     <t>🕓 Pendiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implementar modelo intermedio DetalleOrden para trazabilidad de precios históricos según feedback"</t>
+  </si>
+  <si>
+    <t>Conexion de modelos con vistas y sistema de navegacion funcional</t>
+  </si>
+  <si>
+    <t>Creación 8 registros del modelo artículo y proveedores, falta órdenes de compra</t>
+  </si>
+  <si>
+    <t>Adición nuevo modelo DetalleOrden</t>
   </si>
 </sst>
 </file>
@@ -523,7 +535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -543,37 +555,88 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46132</v>
+      </c>
+      <c r="E5" s="3">
+        <v>46132</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46133</v>
+      </c>
+      <c r="E6" s="3">
+        <v>46133</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46133</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46133</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46134</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46134</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>7</v>
       </c>

--- a/Planificacion_Grupo03_E2.xlsx
+++ b/Planificacion_Grupo03_E2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\IW-GRUPO3-E2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C11D0F3-AB6A-46EB-8644-E87FCEB39ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0325D045-F5A6-4594-A7B9-C318D3B3A8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
   <si>
     <t>Nº</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Adición nuevo modelo DetalleOrden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">implementar dashboard con estadísticas, navegación centralizada y cálculo de totales en órdenes, así como prueba de botón Nuevo Artículo </t>
   </si>
 </sst>
 </file>
@@ -641,13 +644,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2"/>
+    <row r="9" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46139</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46139</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>11</v>
       </c>

--- a/Planificacion_Grupo03_E2.xlsx
+++ b/Planificacion_Grupo03_E2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\IW-GRUPO3-E2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0325D045-F5A6-4594-A7B9-C318D3B3A8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FEA8BE-F065-4771-8A72-B6A897B35B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>Nº</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t xml:space="preserve">implementar dashboard con estadísticas, navegación centralizada y cálculo de totales en órdenes, así como prueba de botón Nuevo Artículo </t>
+  </si>
+  <si>
+    <t>Listado y detalle Proveedores</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -538,7 +541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -668,12 +671,24 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46143</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46143</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>12</v>
       </c>
